--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ce profil représente les professionnels de santé et leurs rôles en FHIR.</t>
+    <t>Ce profil représente les professionnels de santé et leurs rôles dans le cadre d'un document médical.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$162</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4111" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6005" uniqueCount="728">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1834,6 +1834,279 @@
   </si>
   <si>
     <t>SituationExercice.boiteLettresMSS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>as-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
+</t>
+  </si>
+  <si>
+    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
+  </si>
+  <si>
+    <t>Extension contenant les métadonnées de la mailbox mss.</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>typeBAL : Type de boîte aux lettres.
+Valeurs possibles : ORG | APP | PER | CAB</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.extension.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.extension.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
+  </si>
+  <si>
+    <t>responsible</t>
+  </si>
+  <si>
+    <t>responsable : Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>telephone : Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté.</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization</t>
+  </si>
+  <si>
+    <t>digitization</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge</t>
+  </si>
+  <si>
+    <t>listeRouge</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.system</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.value</t>
+  </si>
+  <si>
+    <t>Boîte Aux Lettres (BAL) MSS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.use</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.rank</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -2304,11 +2577,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO110"/>
+  <dimension ref="A1:AO162"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="100.33203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="52.328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="36.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2317,7 +2590,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="108.7421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -13372,7 +13645,7 @@
         <v>590</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>590</v>
+        <v>535</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13383,10 +13656,10 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>78</v>
@@ -13395,17 +13668,15 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>591</v>
+        <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>592</v>
+        <v>105</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13454,19 +13725,19 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>590</v>
+        <v>107</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13475,7 +13746,7 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>595</v>
+        <v>108</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13486,10 +13757,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>596</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13497,10 +13768,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
@@ -13512,13 +13783,13 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13557,31 +13828,31 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -13590,7 +13861,7 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -13601,21 +13872,23 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="D97" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -13627,17 +13900,15 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>539</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>112</v>
+        <v>540</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13707,7 +13978,7 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13718,46 +13989,42 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>599</v>
+        <v>78</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>600</v>
+        <v>105</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13805,19 +14072,19 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>602</v>
+        <v>107</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
@@ -13826,7 +14093,7 @@
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13837,10 +14104,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13851,7 +14118,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13863,13 +14130,13 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>604</v>
+        <v>201</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>605</v>
+        <v>202</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13896,31 +14163,31 @@
         <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>607</v>
+        <v>78</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>603</v>
+        <v>118</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13932,7 +14199,7 @@
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -13941,7 +14208,7 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13952,10 +14219,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13963,7 +14230,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>90</v>
@@ -13978,22 +14245,24 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>325</v>
+        <v>137</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>78</v>
+        <v>602</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>78</v>
@@ -14035,10 +14304,10 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>90</v>
@@ -14047,7 +14316,7 @@
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -14056,7 +14325,7 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>595</v>
+        <v>199</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14067,10 +14336,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14093,17 +14362,15 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>612</v>
+        <v>154</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>615</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14113,7 +14380,7 @@
         <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>78</v>
+        <v>608</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>78</v>
@@ -14128,13 +14395,11 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>78</v>
+        <v>609</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14152,7 +14417,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14173,7 +14438,7 @@
         <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>595</v>
+        <v>199</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14184,12 +14449,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14210,17 +14477,15 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N102" t="s" s="2">
         <v>615</v>
       </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14269,19 +14534,19 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>616</v>
+        <v>118</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14290,7 +14555,7 @@
         <v>78</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -14301,10 +14566,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>619</v>
+        <v>594</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14315,10 +14580,10 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>78</v>
@@ -14327,13 +14592,13 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>591</v>
+        <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>620</v>
+        <v>105</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>621</v>
+        <v>106</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14384,19 +14649,19 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>619</v>
+        <v>107</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
@@ -14405,7 +14670,7 @@
         <v>78</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>595</v>
+        <v>108</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>78</v>
@@ -14416,21 +14681,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -14442,15 +14707,17 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14487,31 +14754,31 @@
         <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
@@ -14531,21 +14798,23 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="D105" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
@@ -14560,14 +14829,12 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>112</v>
+        <v>620</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14637,7 +14904,7 @@
         <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>78</v>
@@ -14648,46 +14915,42 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>599</v>
+        <v>78</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>600</v>
+        <v>105</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14735,19 +14998,19 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>602</v>
+        <v>107</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
@@ -14756,7 +15019,7 @@
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14767,10 +15030,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14778,10 +15041,10 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14793,13 +15056,13 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>626</v>
+        <v>201</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>627</v>
+        <v>202</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14838,31 +15101,31 @@
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>625</v>
+        <v>118</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
@@ -14871,7 +15134,7 @@
         <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14882,10 +15145,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14893,7 +15156,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>90</v>
@@ -14908,22 +15171,24 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>294</v>
+        <v>137</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>629</v>
+        <v>599</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -14965,10 +15230,10 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>628</v>
+        <v>603</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>90</v>
@@ -14977,7 +15242,7 @@
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
@@ -14986,7 +15251,7 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>595</v>
+        <v>199</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14997,10 +15262,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15014,7 +15279,7 @@
         <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>78</v>
@@ -15023,13 +15288,13 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>632</v>
+        <v>606</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>633</v>
+        <v>607</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15056,13 +15321,11 @@
         <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>78</v>
+        <v>629</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -15080,7 +15343,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15101,7 +15364,7 @@
         <v>78</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>595</v>
+        <v>199</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -15112,12 +15375,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C110" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="D110" t="s" s="2">
         <v>78</v>
       </c>
@@ -15126,10 +15391,10 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>78</v>
@@ -15138,18 +15403,16 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>635</v>
+        <v>111</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>636</v>
+        <v>201</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>637</v>
+        <v>202</v>
       </c>
       <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>638</v>
-      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -15197,7 +15460,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>634</v>
+        <v>118</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15209,26 +15472,6060 @@
         <v>78</v>
       </c>
       <c r="AJ110" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM110" t="s" s="2">
+      <c r="AK114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM116" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AN110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO110" t="s" s="2">
+      <c r="AN116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="D125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="D130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="D135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO141" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AO142" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="149" hidden="true">
+      <c r="A149" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="150" hidden="true">
+      <c r="A150" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="151" hidden="true">
+      <c r="A151" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
+      <c r="P155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="157" hidden="true">
+      <c r="A157" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="160" hidden="true">
+      <c r="A160" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="161" hidden="true">
+      <c r="A161" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
+      <c r="P161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO161" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="162" hidden="true">
+      <c r="A162" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N162" s="2"/>
+      <c r="O162" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="P162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO162" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO110">
+  <autoFilter ref="A1:AO162">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15238,7 +21535,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI109">
+  <conditionalFormatting sqref="A2:AI161">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$110</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6005" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4111" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1834,279 +1834,6 @@
   </si>
   <si>
     <t>SituationExercice.boiteLettresMSS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
-  &lt;code value="MSSANTE"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>as-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
-</t>
-  </si>
-  <si>
-    <t>Les attributs 'responsible' et 'phone' ne sont pas disponibles en accès libre.</t>
-  </si>
-  <si>
-    <t>Extension contenant les métadonnées de la mailbox mss.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>typeBAL : Type de boîte aux lettres.
-Valeurs possibles : ORG | APP | PER | CAB</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible</t>
-  </si>
-  <si>
-    <t>responsible</t>
-  </si>
-  <si>
-    <t>responsable : Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service</t>
-  </si>
-  <si>
-    <t>service</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:service.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>telephone : Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté.</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization</t>
-  </si>
-  <si>
-    <t>digitization</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:digitization.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge</t>
-  </si>
-  <si>
-    <t>listeRouge</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:listeRouge.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.system</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.value</t>
-  </si>
-  <si>
-    <t>Boîte Aux Lettres (BAL) MSS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.rank</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom:mailbox-mss.period</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -2577,20 +2304,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO162"/>
+  <dimension ref="A1:AO110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="100.33203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="52.328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.3984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.48046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="31.20703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.2265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2599,27 +2326,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="105.0546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="89.67578125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.96875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="90.06640625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="76.87890625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.26953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="65.859375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="85.47265625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="194.47265625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="56.46484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="73.27734375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="166.7265625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13645,7 +13372,7 @@
         <v>590</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>535</v>
+        <v>590</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13656,10 +13383,10 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>78</v>
@@ -13668,15 +13395,17 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>104</v>
+        <v>591</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>105</v>
+        <v>592</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13725,19 +13454,19 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>107</v>
+        <v>590</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13746,7 +13475,7 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>108</v>
+        <v>595</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13757,10 +13486,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>536</v>
+        <v>596</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13768,11 +13497,11 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G96" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13783,13 +13512,13 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13828,31 +13557,31 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -13861,7 +13590,7 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -13872,23 +13601,21 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -13900,15 +13627,17 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>539</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>540</v>
+        <v>112</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13978,7 +13707,7 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13989,42 +13718,46 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>78</v>
+        <v>599</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>105</v>
+        <v>600</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -14072,19 +13805,19 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>107</v>
+        <v>602</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
@@ -14093,7 +13826,7 @@
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -14104,10 +13837,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14118,7 +13851,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -14130,13 +13863,13 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>201</v>
+        <v>604</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>202</v>
+        <v>605</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14163,31 +13896,31 @@
         <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>78</v>
+        <v>606</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>78</v>
+        <v>607</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>118</v>
+        <v>603</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14199,7 +13932,7 @@
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -14208,7 +13941,7 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -14219,10 +13952,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14230,7 +13963,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>90</v>
@@ -14245,24 +13978,22 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>137</v>
+        <v>325</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>602</v>
+        <v>78</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>78</v>
@@ -14304,10 +14035,10 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>90</v>
@@ -14316,7 +14047,7 @@
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -14325,7 +14056,7 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>199</v>
+        <v>595</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14336,10 +14067,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14362,15 +14093,17 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>154</v>
+        <v>612</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14380,7 +14113,7 @@
         <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>608</v>
+        <v>78</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>78</v>
@@ -14395,11 +14128,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14417,7 +14152,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14438,7 +14173,7 @@
         <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>199</v>
+        <v>595</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14449,14 +14184,12 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>612</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14477,15 +14210,17 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="M102" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14534,19 +14269,19 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>118</v>
+        <v>616</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14555,7 +14290,7 @@
         <v>78</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -14566,10 +14301,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14580,10 +14315,10 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>78</v>
@@ -14592,13 +14327,13 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>104</v>
+        <v>591</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>105</v>
+        <v>620</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>106</v>
+        <v>621</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14649,19 +14384,19 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>107</v>
+        <v>619</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
@@ -14670,7 +14405,7 @@
         <v>78</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>108</v>
+        <v>595</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>78</v>
@@ -14681,21 +14416,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -14707,17 +14442,15 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14754,31 +14487,31 @@
         <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
@@ -14798,23 +14531,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
@@ -14829,12 +14560,14 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>620</v>
+        <v>112</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14904,7 +14637,7 @@
         <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>78</v>
@@ -14915,42 +14648,46 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>78</v>
+        <v>599</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>105</v>
+        <v>600</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14998,19 +14735,19 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>107</v>
+        <v>602</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
@@ -15019,7 +14756,7 @@
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -15030,10 +14767,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15041,10 +14778,10 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -15056,13 +14793,13 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>201</v>
+        <v>626</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>202</v>
+        <v>627</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15101,31 +14838,31 @@
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>118</v>
+        <v>625</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
@@ -15134,7 +14871,7 @@
         <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -15145,10 +14882,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15156,7 +14893,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>90</v>
@@ -15171,24 +14908,22 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>137</v>
+        <v>294</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>619</v>
+        <v>78</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -15230,10 +14965,10 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>90</v>
@@ -15242,7 +14977,7 @@
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
@@ -15251,7 +14986,7 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>199</v>
+        <v>595</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -15262,10 +14997,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15279,7 +15014,7 @@
         <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>78</v>
@@ -15288,13 +15023,13 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>261</v>
+        <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>606</v>
+        <v>632</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>607</v>
+        <v>633</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15321,11 +15056,13 @@
         <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y109" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z109" t="s" s="2">
-        <v>629</v>
+        <v>78</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -15343,7 +15080,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15364,7 +15101,7 @@
         <v>78</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>199</v>
+        <v>595</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -15375,14 +15112,12 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>631</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>78</v>
       </c>
@@ -15391,10 +15126,10 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>78</v>
@@ -15403,16 +15138,18 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>111</v>
+        <v>635</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>201</v>
+        <v>636</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>202</v>
+        <v>637</v>
       </c>
       <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -15460,7 +15197,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>118</v>
+        <v>634</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15472,7 +15209,7 @@
         <v>78</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>78</v>
@@ -15481,6051 +15218,17 @@
         <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="D115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C120" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="D120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="D125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="D130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="D135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="P143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="145" hidden="true">
-      <c r="A145" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G145" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="O145" s="2"/>
-      <c r="P145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q145" s="2"/>
-      <c r="R145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="146" hidden="true">
-      <c r="A146" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E146" s="2"/>
-      <c r="F146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G146" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
-      <c r="P146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q146" s="2"/>
-      <c r="R146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="147" hidden="true">
-      <c r="A147" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E147" s="2"/>
-      <c r="F147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H147" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K147" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="O147" s="2"/>
-      <c r="P147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q147" s="2"/>
-      <c r="R147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="AG147" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="148" hidden="true">
-      <c r="A148" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E148" s="2"/>
-      <c r="F148" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" s="2"/>
-      <c r="R148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O149" s="2"/>
-      <c r="P149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="150" hidden="true">
-      <c r="A150" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
-      <c r="P152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="O154" s="2"/>
-      <c r="P154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
-      <c r="P155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
-      <c r="P156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="157" hidden="true">
-      <c r="A157" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O157" s="2"/>
-      <c r="P157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="158" hidden="true">
-      <c r="A158" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q158" s="2"/>
-      <c r="R158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="159" hidden="true">
-      <c r="A159" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" s="2"/>
-      <c r="P159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="160" hidden="true">
-      <c r="A160" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
-      <c r="P160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="161" hidden="true">
-      <c r="A161" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C161" s="2"/>
-      <c r="D161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N161" s="2"/>
-      <c r="O161" s="2"/>
-      <c r="P161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO161" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="162" hidden="true">
-      <c r="A162" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="C162" s="2"/>
-      <c r="D162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E162" s="2"/>
-      <c r="F162" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="P162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q162" s="2"/>
-      <c r="R162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO162" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO162">
+  <autoFilter ref="A1:AO110">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21535,7 +15238,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI161">
+  <conditionalFormatting sqref="A2:AI109">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
